--- a/data/trans_dic/P1416-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1416-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,81</t>
+          <t>3,68; 6,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,92</t>
+          <t>2,92; 6,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,29</t>
+          <t>3,04; 6,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 12,07</t>
+          <t>6,87; 11,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,82</t>
+          <t>6,63; 10,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,77</t>
+          <t>4,69; 8,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,74</t>
+          <t>4,07; 7,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 14,62</t>
+          <t>10,09; 14,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,2</t>
+          <t>5,54; 8,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,7</t>
+          <t>4,07; 6,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,33</t>
+          <t>3,86; 6,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 12,66</t>
+          <t>9,1; 12,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 9,32</t>
+          <t>5,71; 9,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,39</t>
+          <t>4,28; 7,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,97</t>
+          <t>3,33; 5,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,17</t>
+          <t>7,45; 11,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,85</t>
+          <t>8,0; 12,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,62</t>
+          <t>6,15; 9,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 11,29</t>
+          <t>7,72; 11,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 11,97</t>
+          <t>8,92; 12,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,92</t>
+          <t>7,34; 10,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,03</t>
+          <t>5,73; 7,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,13</t>
+          <t>5,94; 8,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,91</t>
+          <t>8,68; 11,5</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,13</t>
+          <t>4,43; 8,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,35</t>
+          <t>3,76; 7,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,11</t>
+          <t>2,32; 5,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 15,93</t>
+          <t>9,38; 14,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 10,96</t>
+          <t>6,94; 11,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,42</t>
+          <t>4,89; 8,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,33</t>
+          <t>6,04; 10,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 13,2</t>
+          <t>11,25; 15,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,85</t>
+          <t>6,09; 8,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,42</t>
+          <t>4,7; 7,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,19</t>
+          <t>4,74; 7,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 13,29</t>
+          <t>10,98; 14,5</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,42</t>
+          <t>5,96; 9,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,49</t>
+          <t>3,75; 6,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,98</t>
+          <t>5,5; 8,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,73</t>
+          <t>7,04; 10,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 12,65</t>
+          <t>8,72; 12,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 9,89</t>
+          <t>6,54; 9,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,71</t>
+          <t>6,32; 9,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,43</t>
+          <t>10,62; 14,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 10,54</t>
+          <t>7,89; 10,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 7,76</t>
+          <t>5,59; 7,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,73</t>
+          <t>6,34; 8,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,83</t>
+          <t>9,43; 12,16</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,63</t>
+          <t>5,76; 7,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,93</t>
+          <t>4,37; 5,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,78</t>
+          <t>4,24; 5,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 10,98</t>
+          <t>8,57; 10,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 10,59</t>
+          <t>8,64; 10,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,26</t>
+          <t>6,47; 8,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 8,8</t>
+          <t>7,07; 8,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,79; 12,09</t>
+          <t>11,07; 13,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,88</t>
+          <t>7,51; 8,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,89</t>
+          <t>5,71; 6,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,15</t>
+          <t>5,88; 7,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,14</t>
+          <t>10,11; 11,61</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57481</t>
+          <t>61478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83181</t>
+          <t>88110</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>140662</t>
+          <t>149588</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25670; 47287</t>
+          <t>25552; 47983</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19074; 41587</t>
+          <t>20477; 42922</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20729; 42440</t>
+          <t>20527; 42066</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42934; 76714</t>
+          <t>47427; 80039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46352; 74495</t>
+          <t>45603; 73111</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33734; 61112</t>
+          <t>32687; 60075</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27251; 52051</t>
+          <t>27367; 51901</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>69764; 98437</t>
+          <t>73712; 104619</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>75677; 113411</t>
+          <t>76568; 114183</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59033; 93752</t>
+          <t>56976; 91503</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52275; 85303</t>
+          <t>52079; 85066</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>121223; 165632</t>
+          <t>129277; 173297</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96593</t>
+          <t>99781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98430</t>
+          <t>112103</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>195023</t>
+          <t>211884</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56565; 89679</t>
+          <t>54949; 88228</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43407; 75223</t>
+          <t>43611; 75034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34418; 61006</t>
+          <t>34001; 60921</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43067; 133294</t>
+          <t>78152; 125419</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75669; 114714</t>
+          <t>77498; 116306</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64397; 99172</t>
+          <t>63369; 100721</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79043; 117765</t>
+          <t>80468; 116763</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84121; 114272</t>
+          <t>95205; 130988</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>142323; 191567</t>
+          <t>141598; 193054</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116671; 164441</t>
+          <t>117332; 163659</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120973; 167995</t>
+          <t>122781; 168127</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>122879; 234263</t>
+          <t>183589; 243358</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86762</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87828</t>
+          <t>107383</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>174591</t>
+          <t>201680</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28483; 55151</t>
+          <t>30071; 56571</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27921; 55669</t>
+          <t>28482; 56819</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17100; 38807</t>
+          <t>17630; 38109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67139; 111663</t>
+          <t>75005; 116505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46846; 74951</t>
+          <t>47477; 75984</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37238; 65442</t>
+          <t>37967; 65319</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50225; 81068</t>
+          <t>47434; 78892</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43507; 122272</t>
+          <t>90567; 125783</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82754; 120521</t>
+          <t>82990; 121072</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74139; 113895</t>
+          <t>72112; 113834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74160; 111127</t>
+          <t>73167; 111197</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>111125; 216271</t>
+          <t>176173; 232662</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84179</t>
+          <t>87373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>123553</t>
+          <t>137586</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>207731</t>
+          <t>224959</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57445; 88746</t>
+          <t>56185; 89228</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34611; 61541</t>
+          <t>35574; 61889</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51254; 84174</t>
+          <t>51601; 83006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65648; 108482</t>
+          <t>69529; 107644</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91544; 131426</t>
+          <t>90614; 133265</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68395; 104016</t>
+          <t>68760; 104811</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64739; 101331</t>
+          <t>66010; 103026</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>98084; 146291</t>
+          <t>118456; 159450</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>157557; 208752</t>
+          <t>156297; 206246</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111382; 155076</t>
+          <t>111723; 155583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124264; 172924</t>
+          <t>125570; 174806</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>175706; 238225</t>
+          <t>198290; 255748</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325015</t>
+          <t>342929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>392992</t>
+          <t>445182</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>718007</t>
+          <t>788111</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>193186; 249909</t>
+          <t>188622; 250643</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>150737; 203071</t>
+          <t>149764; 203598</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142682; 196124</t>
+          <t>143896; 193843</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>255310; 379206</t>
+          <t>302109; 386344</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>290318; 357888</t>
+          <t>291854; 358099</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>229317; 293884</t>
+          <t>230262; 293374</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>242891; 311813</t>
+          <t>250472; 315818</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>320292; 440376</t>
+          <t>411567; 484539</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>501629; 590728</t>
+          <t>499853; 593898</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>398486; 481127</t>
+          <t>398827; 481472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>409329; 495829</t>
+          <t>408350; 493309</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>623311; 790962</t>
+          <t>732522; 840964</t>
         </is>
       </c>
     </row>
